--- a/Starfront/文档/配置表/__beans__.xlsx
+++ b/Starfront/文档/配置表/__beans__.xlsx
@@ -5152,1175 +5152,1382 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="6.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="40" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7" style="1" customWidth="1"/>
-    <col min="14" max="14" width="58" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="25"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="25"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="26"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="3"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="27"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="2:16">
-      <c r="B12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="28"/>
-    </row>
-    <row r="14" spans="2:16">
-      <c r="B14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="28"/>
-    </row>
-    <row r="16" spans="2:16">
-      <c r="B16" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="28"/>
-    </row>
-    <row r="18" spans="2:16">
-      <c r="B18" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="28"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="O20" s="16"/>
-      <c r="P20" s="29"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K21" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="O21" s="19"/>
-      <c r="P21" s="30"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="O23" s="16"/>
-      <c r="P23" s="29"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="K24" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="L24" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="O24" s="23"/>
-      <c r="P24" s="31"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="L25" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="O25" s="23"/>
-      <c r="P25" s="31"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="K26" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="L26" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="O26" s="23"/>
-      <c r="P26" s="31"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="L27" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="O27" s="23"/>
-      <c r="P27" s="31"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="17"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="O28" s="19"/>
-      <c r="P28" s="30"/>
-    </row>
-    <row spans="1:16" r="30">
-      <c r="A30" s="32"/>
-      <c r="B30" s="33" t="str">
-        <v>bean.CardContent</v>
-      </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="37" t="str">
-        <v>卡牌内容</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="47"/>
-    </row>
-    <row spans="1:16" r="32">
-      <c r="A32" s="48"/>
-      <c r="B32" s="49" t="str">
-        <v>UnitCardContent</v>
-      </c>
-      <c r="C32" s="50" t="str">
-        <v>bean.CardContent</v>
-      </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="53" t="str">
-        <v>兵种卡</v>
-      </c>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="57" t="str">
-        <v>unitId</v>
-      </c>
-      <c r="K32" s="58" t="str">
-        <v>兵种ID</v>
-      </c>
-      <c r="L32" s="59" t="str">
-        <v>int</v>
-      </c>
-      <c r="M32" s="60"/>
-      <c r="N32" s="61" t="inlineStr">
-        <is>
-          <t>引用UnitResource.id；经生产配置关联生产建筑</t>
-        </is>
-      </c>
-      <c r="O32" s="62"/>
-      <c r="P32" s="63"/>
-    </row>
-    <row spans="1:16" r="34">
-      <c r="A34" s="64"/>
-      <c r="B34" s="65" t="str">
-        <v>BuildingCardContent</v>
-      </c>
-      <c r="C34" s="66" t="str">
-        <v>bean.CardContent</v>
-      </c>
-      <c r="D34" s="67"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69" t="str">
-        <v>建筑卡</v>
-      </c>
-      <c r="G34" s="70"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="73" t="str">
-        <v>buildingId</v>
-      </c>
-      <c r="K34" s="74" t="str">
-        <v>建筑ID</v>
-      </c>
-      <c r="L34" s="75" t="str">
-        <v>int</v>
-      </c>
-      <c r="M34" s="76"/>
-      <c r="N34" s="77" t="inlineStr">
-        <is>
-          <t>引用BuildingResource.id；不配置基地或重复生产建筑卡</t>
-        </is>
-      </c>
-      <c r="O34" s="78"/>
-      <c r="P34" s="79"/>
-    </row>
-    <row spans="1:16" r="36">
-      <c r="A36" s="80"/>
-      <c r="B36" s="81" t="str">
-        <v>bean.BuildingAppearance</v>
-      </c>
-      <c r="C36" s="82"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="85" t="str">
-        <v>建筑外观</v>
-      </c>
-      <c r="G36" s="86"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="88"/>
-      <c r="J36" s="89" t="str">
-        <v>direction</v>
-      </c>
-      <c r="K36" s="90" t="str">
-        <v>朝向</v>
-      </c>
-      <c r="L36" s="91" t="str">
-        <v>BuildingAppearanceDirection</v>
-      </c>
-      <c r="M36" s="92"/>
-      <c r="N36" s="93" t="str">
-        <v>固定或上下朝向；不表示敌我阵营</v>
-      </c>
-      <c r="O36" s="94"/>
-      <c r="P36" s="95"/>
-    </row>
-    <row spans="1:16" r="37">
-      <c r="A37" s="96"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="105" t="str">
-        <v>part</v>
-      </c>
-      <c r="K37" s="106" t="str">
-        <v>外观部件</v>
-      </c>
-      <c r="L37" s="107" t="str">
-        <v>BuildingAppearancePart</v>
-      </c>
-      <c r="M37" s="108"/>
-      <c r="N37" s="109" t="str">
-        <v>主体、底座、炮身或独立地面阴影</v>
-      </c>
-      <c r="O37" s="110"/>
-      <c r="P37" s="111"/>
-    </row>
-    <row spans="1:16" r="38">
-      <c r="A38" s="112"/>
-      <c r="B38" s="113"/>
-      <c r="C38" s="114"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="119"/>
-      <c r="I38" s="120"/>
-      <c r="J38" s="121" t="str">
-        <v>resourceType</v>
-      </c>
-      <c r="K38" s="122" t="str">
-        <v>资源类型</v>
-      </c>
-      <c r="L38" s="123" t="str">
-        <v>BattleSceneResourceType</v>
-      </c>
-      <c r="M38" s="124"/>
-      <c r="N38" s="125" t="str">
-        <v>复用静态图片与帧动画资源类型</v>
-      </c>
-      <c r="O38" s="126"/>
-      <c r="P38" s="127"/>
-    </row>
-    <row spans="1:16" r="39">
-      <c r="A39" s="128"/>
-      <c r="B39" s="129"/>
-      <c r="C39" s="130"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="134"/>
-      <c r="H39" s="135"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="137" t="str">
-        <v>resource</v>
-      </c>
-      <c r="K39" s="138" t="str">
-        <v>资源引用</v>
-      </c>
-      <c r="L39" s="139" t="str">
-        <v>string</v>
-      </c>
-      <c r="M39" s="140"/>
-      <c r="N39" s="141" t="str">
-        <v>相对Assets/Art/unpack/；不填固定后缀</v>
-      </c>
-      <c r="O39" s="142"/>
-      <c r="P39" s="143"/>
-    </row>
-    <row spans="1:16" r="40">
-      <c r="A40" s="144"/>
-      <c r="B40" s="145"/>
-      <c r="C40" s="146"/>
-      <c r="D40" s="147"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="150"/>
-      <c r="H40" s="151"/>
-      <c r="I40" s="152"/>
-      <c r="J40" s="153" t="str">
-        <v>offset</v>
-      </c>
-      <c r="K40" s="154" t="str">
-        <v>显示偏移</v>
-      </c>
-      <c r="L40" s="155" t="str">
-        <v>vector2</v>
-      </c>
-      <c r="M40" s="156"/>
-      <c r="N40" s="157" t="str">
-        <v>相对建筑定位锚点；设计像素，X右Y下</v>
-      </c>
-      <c r="O40" s="158"/>
-      <c r="P40" s="159"/>
-    </row>
-    <row spans="1:16" r="42">
-      <c r="A42" s="160"/>
-      <c r="B42" s="161" t="str">
-        <v>bean.UnitAppearance</v>
-      </c>
-      <c r="C42" s="162"/>
-      <c r="D42" s="163"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="165" t="str">
-        <v>兵种外观</v>
-      </c>
-      <c r="G42" s="166"/>
-      <c r="H42" s="167"/>
-      <c r="I42" s="168"/>
-      <c r="J42" s="169" t="str">
-        <v>action</v>
-      </c>
-      <c r="K42" s="170" t="str">
-        <v>动作</v>
-      </c>
-      <c r="L42" s="171" t="str">
-        <v>UnitActionType</v>
-      </c>
-      <c r="M42" s="172"/>
-      <c r="N42" s="173" t="str">
-        <v>移动、死亡、攻击动作1；后续按技能扩展</v>
-      </c>
-      <c r="O42" s="174"/>
-      <c r="P42" s="175"/>
-    </row>
-    <row spans="1:16" r="43">
-      <c r="A43" s="176"/>
-      <c r="B43" s="177"/>
-      <c r="C43" s="178"/>
-      <c r="D43" s="179"/>
-      <c r="E43" s="180"/>
-      <c r="F43" s="181"/>
-      <c r="G43" s="182"/>
-      <c r="H43" s="183"/>
-      <c r="I43" s="184"/>
-      <c r="J43" s="185" t="str">
-        <v>direction</v>
-      </c>
-      <c r="K43" s="186" t="str">
-        <v>源朝向</v>
-      </c>
-      <c r="L43" s="187" t="str">
-        <v>UnitAppearanceDirection</v>
-      </c>
-      <c r="M43" s="188"/>
-      <c r="N43" s="189" t="str">
-        <v>仅配五个源朝向；左侧由右侧水平镜像</v>
-      </c>
-      <c r="O43" s="190"/>
-      <c r="P43" s="191"/>
-    </row>
-    <row spans="1:16" r="44">
-      <c r="A44" s="192"/>
-      <c r="B44" s="193"/>
-      <c r="C44" s="194"/>
-      <c r="D44" s="195"/>
-      <c r="E44" s="196"/>
-      <c r="F44" s="197"/>
-      <c r="G44" s="198"/>
-      <c r="H44" s="199"/>
-      <c r="I44" s="200"/>
-      <c r="J44" s="201" t="str">
-        <v>resource</v>
-      </c>
-      <c r="K44" s="202" t="str">
-        <v>动画资源</v>
-      </c>
-      <c r="L44" s="203" t="str">
-        <v>string</v>
-      </c>
-      <c r="M44" s="204"/>
-      <c r="N44" s="205" t="str">
-        <v>相对Assets/Art/frameAnimation/的动画资源标识</v>
-      </c>
-      <c r="O44" s="206"/>
-      <c r="P44" s="207"/>
-    </row>
-    <row spans="1:16" r="45">
-      <c r="A45" s="208"/>
-      <c r="B45" s="209"/>
-      <c r="C45" s="210"/>
-      <c r="D45" s="211"/>
-      <c r="E45" s="212"/>
-      <c r="F45" s="213"/>
-      <c r="G45" s="214"/>
-      <c r="H45" s="215"/>
-      <c r="I45" s="216"/>
-      <c r="J45" s="217" t="str">
-        <v>loop</v>
-      </c>
-      <c r="K45" s="218" t="str">
-        <v>循环播放</v>
-      </c>
-      <c r="L45" s="219" t="str">
-        <v>bool</v>
-      </c>
-      <c r="M45" s="220"/>
-      <c r="N45" s="221" t="str">
-        <v>移动循环；其他动作分别确定播放方式</v>
-      </c>
-      <c r="O45" s="222"/>
-      <c r="P45" s="223"/>
-    </row>
-    <row spans="1:16" r="46">
-      <c r="A46" s="224"/>
-      <c r="B46" s="225"/>
-      <c r="C46" s="226"/>
-      <c r="D46" s="227"/>
-      <c r="E46" s="228"/>
-      <c r="F46" s="229"/>
-      <c r="G46" s="230"/>
-      <c r="H46" s="231"/>
-      <c r="I46" s="232"/>
-      <c r="J46" s="233" t="str">
-        <v>offset</v>
-      </c>
-      <c r="K46" s="234" t="str">
-        <v>显示偏移</v>
-      </c>
-      <c r="L46" s="235" t="str">
-        <v>vector2</v>
-      </c>
-      <c r="M46" s="236"/>
-      <c r="N46" s="237" t="str">
-        <v>相对地面定位点；设计像素，X右Y下</v>
-      </c>
-      <c r="O46" s="238"/>
-      <c r="P46" s="239"/>
-    </row>
-    <row spans="1:16" r="48">
-      <c r="A48" s="240"/>
-      <c r="B48" s="241" t="str">
-        <v>bean.ItemCost</v>
-      </c>
-      <c r="C48" s="242"/>
-      <c r="D48" s="243"/>
-      <c r="E48" s="244"/>
-      <c r="F48" s="245" t="str">
-        <v>道具消耗</v>
-      </c>
-      <c r="G48" s="246"/>
-      <c r="H48" s="247"/>
-      <c r="I48" s="248"/>
-      <c r="J48" s="249" t="str">
-        <v>itemId</v>
-      </c>
-      <c r="K48" s="250" t="str">
-        <v>道具ID</v>
-      </c>
-      <c r="L48" s="251" t="str">
-        <v>int</v>
-      </c>
-      <c r="M48" s="252"/>
-      <c r="N48" s="253" t="str">
-        <v>引用ItemResource.id；碎片或指定局外货币</v>
-      </c>
-      <c r="O48" s="254"/>
-      <c r="P48" s="255"/>
-    </row>
-    <row spans="1:16" r="49">
-      <c r="A49" s="256"/>
-      <c r="B49" s="257"/>
-      <c r="C49" s="258"/>
-      <c r="D49" s="259"/>
-      <c r="E49" s="260"/>
-      <c r="F49" s="261"/>
-      <c r="G49" s="262"/>
-      <c r="H49" s="263"/>
-      <c r="I49" s="264"/>
-      <c r="J49" s="265" t="str">
-        <v>count</v>
-      </c>
-      <c r="K49" s="266" t="str">
-        <v>消耗数量</v>
-      </c>
-      <c r="L49" s="267" t="str">
-        <v>double</v>
-      </c>
-      <c r="M49" s="268"/>
-      <c r="N49" s="269" t="str">
-        <v>有限正数；碎片须为整数，不含局内货币</v>
-      </c>
-      <c r="O49" s="270"/>
-      <c r="P49" s="271"/>
-    </row>
-    <row spans="1:16" r="51">
-      <c r="A51" s="272"/>
-      <c r="B51" s="273" t="str">
-        <v>bean.BattleDeckCard</v>
-      </c>
-      <c r="C51" s="274"/>
-      <c r="D51" s="275"/>
-      <c r="E51" s="276"/>
-      <c r="F51" s="277" t="str">
-        <v>卡组卡牌</v>
-      </c>
-      <c r="G51" s="278"/>
-      <c r="H51" s="279"/>
-      <c r="I51" s="280"/>
-      <c r="J51" s="281" t="str">
-        <v>cardId</v>
-      </c>
-      <c r="K51" s="282" t="str">
-        <v>卡牌ID</v>
-      </c>
-      <c r="L51" s="283" t="str">
-        <v>int</v>
-      </c>
-      <c r="M51" s="284"/>
-      <c r="N51" s="285" t="str">
-        <v>引用CardResource.id；卡组内不得重复</v>
-      </c>
-      <c r="O51" s="286"/>
-      <c r="P51" s="287"/>
-    </row>
-    <row spans="1:16" r="52">
-      <c r="A52" s="288"/>
-      <c r="B52" s="289"/>
-      <c r="C52" s="290"/>
-      <c r="D52" s="291"/>
-      <c r="E52" s="292"/>
-      <c r="F52" s="293"/>
-      <c r="G52" s="294"/>
-      <c r="H52" s="295"/>
-      <c r="I52" s="296"/>
-      <c r="J52" s="297" t="str">
-        <v>locked</v>
-      </c>
-      <c r="K52" s="298" t="str">
-        <v>固定槽位</v>
-      </c>
-      <c r="L52" s="299" t="str">
-        <v>bool</v>
-      </c>
-      <c r="M52" s="300"/>
-      <c r="N52" s="301" t="str">
-        <v>不可移除替换，仍占槽位</v>
-      </c>
-      <c r="O52" s="302"/>
-      <c r="P52" s="303"/>
-    </row>
-    <row spans="1:16" r="54">
-      <c r="A54" s="304"/>
-      <c r="B54" s="305" t="str">
-        <v>bean.UnitQualityWeight</v>
-      </c>
-      <c r="C54" s="306"/>
-      <c r="D54" s="307"/>
-      <c r="E54" s="308"/>
-      <c r="F54" s="309" t="str">
-        <v>兵种品质权重</v>
-      </c>
-      <c r="G54" s="310"/>
-      <c r="H54" s="311"/>
-      <c r="I54" s="312"/>
-      <c r="J54" s="313" t="str">
-        <v>quality</v>
-      </c>
-      <c r="K54" s="314" t="str">
-        <v>品质</v>
-      </c>
-      <c r="L54" s="315" t="str">
-        <v>Quality</v>
-      </c>
-      <c r="M54" s="316"/>
-      <c r="N54" s="317" t="str">
-        <v>本局兵种卡候选品质，不含普通</v>
-      </c>
-      <c r="O54" s="318"/>
-      <c r="P54" s="319"/>
-    </row>
-    <row spans="1:16" r="55">
-      <c r="A55" s="320"/>
-      <c r="B55" s="321"/>
-      <c r="C55" s="322"/>
-      <c r="D55" s="323"/>
-      <c r="E55" s="324"/>
-      <c r="F55" s="325"/>
-      <c r="G55" s="326"/>
-      <c r="H55" s="327"/>
-      <c r="I55" s="328"/>
-      <c r="J55" s="329" t="str">
-        <v>weight</v>
-      </c>
-      <c r="K55" s="330" t="str">
-        <v>权重</v>
-      </c>
-      <c r="L55" s="331" t="str">
-        <v>int</v>
-      </c>
-      <c r="M55" s="332"/>
-      <c r="N55" s="333" t="str">
-        <v>结果池相对权重；仅填正值</v>
-      </c>
-      <c r="O55" s="334"/>
-      <c r="P55" s="335"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J1:P1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="$A1:$XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"bean.BattleLastingEffect"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"bean.Effect"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"bean.Condition"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:P66"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="12" customWidth="1"/>
+    <ns0:col min="2" max="2" width="30" customWidth="1"/>
+    <ns0:col min="3" max="3" width="30" customWidth="1"/>
+    <ns0:col min="4" max="4" width="13" customWidth="1"/>
+    <ns0:col min="5" max="5" width="12" customWidth="1"/>
+    <ns0:col min="6" max="6" width="20" customWidth="1"/>
+    <ns0:col min="7" max="7" width="22" customWidth="1"/>
+    <ns0:col min="8" max="8" width="12" customWidth="1"/>
+    <ns0:col min="9" max="9" width="12" customWidth="1"/>
+    <ns0:col min="10" max="10" width="16" customWidth="1"/>
+    <ns0:col min="11" max="11" width="12" customWidth="1"/>
+    <ns0:col min="12" max="12" width="34" customWidth="1"/>
+    <ns0:col min="13" max="13" width="12" customWidth="1"/>
+    <ns0:col min="14" max="14" width="55" customWidth="1"/>
+    <ns0:col min="15" max="15" width="12" customWidth="1"/>
+    <ns0:col min="16" max="16" width="12" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" spans="1:10">
+      <ns0:c r="A1" s="2" t="str">
+        <ns0:v>##var</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="str">
+        <ns0:v>full_name</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="str">
+        <ns0:v>parent</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="str">
+        <ns0:v>valueType</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="str">
+        <ns0:v>sep</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="str">
+        <ns0:v>alias</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="str">
+        <ns0:v>comment</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="1" t="str">
+        <ns0:v>group</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="1" t="str">
+        <ns0:v>tags</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" s="24" t="str">
+        <ns0:v>*fields</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" spans="1:16">
+      <ns0:c r="A2" s="2" t="str">
+        <ns0:v>##var</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" s="1" t="str">
+        <ns0:v>name</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" s="1" t="str">
+        <ns0:v>alias</ns0:v>
+      </ns0:c>
+      <ns0:c r="L2" s="1" t="str">
+        <ns0:v>type</ns0:v>
+      </ns0:c>
+      <ns0:c r="M2" s="1" t="str">
+        <ns0:v>group</ns0:v>
+      </ns0:c>
+      <ns0:c r="N2" s="1" t="str">
+        <ns0:v>comment</ns0:v>
+      </ns0:c>
+      <ns0:c r="O2" s="1" t="str">
+        <ns0:v>tags</ns0:v>
+      </ns0:c>
+      <ns0:c r="P2" s="1" t="str">
+        <ns0:v>variants</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" spans="1:16">
+      <ns0:c r="A3" s="1" t="str">
+        <ns0:v>##</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="str">
+        <ns0:v>全名(包含模块和名字)</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="str">
+        <ns0:v>分割符</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" s="1" t="str">
+        <ns0:v>字段名</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" s="1" t="str">
+        <ns0:v>字段别名</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" s="1" t="str">
+        <ns0:v>类型</ns0:v>
+      </ns0:c>
+      <ns0:c r="M3" s="1" t="str">
+        <ns0:v>分组</ns0:v>
+      </ns0:c>
+      <ns0:c r="N3" s="1" t="str">
+        <ns0:v>注释</ns0:v>
+      </ns0:c>
+      <ns0:c r="P3" s="1" t="str">
+        <ns0:v>字段变体</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" spans="1:16">
+      <ns0:c r="A4" s="0"/>
+      <ns0:c r="B4" s="0"/>
+      <ns0:c r="C4" s="0"/>
+      <ns0:c r="D4" s="0"/>
+      <ns0:c r="E4" s="0"/>
+      <ns0:c r="F4" s="0"/>
+      <ns0:c r="G4" s="0"/>
+      <ns0:c r="H4" s="0"/>
+      <ns0:c r="I4" s="0"/>
+      <ns0:c r="J4" s="0"/>
+      <ns0:c r="K4" s="0"/>
+      <ns0:c r="L4" s="0"/>
+      <ns0:c r="M4" s="0"/>
+      <ns0:c r="N4" s="0"/>
+      <ns0:c r="O4" s="0"/>
+      <ns0:c r="P4" s="0"/>
+    </ns0:row>
+    <ns0:row r="5" spans="1:16">
+      <ns0:c r="A5" s="3"/>
+      <ns0:c r="B5" s="4" t="str">
+        <ns0:v>Shape</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="5"/>
+      <ns0:c r="D5" s="5"/>
+      <ns0:c r="E5" s="5"/>
+      <ns0:c r="F5" s="5"/>
+      <ns0:c r="G5" s="5" t="str">
+        <ns0:v>通用形状基类</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" s="5"/>
+      <ns0:c r="I5" s="5"/>
+      <ns0:c r="J5" s="5"/>
+      <ns0:c r="K5" s="5"/>
+      <ns0:c r="L5" s="5"/>
+      <ns0:c r="M5" s="5"/>
+      <ns0:c r="N5" s="5"/>
+      <ns0:c r="O5" s="5"/>
+      <ns0:c r="P5" s="25"/>
+    </ns0:row>
+    <ns0:row r="6" spans="1:16">
+      <ns0:c r="A6" s="0"/>
+      <ns0:c r="B6" s="0"/>
+      <ns0:c r="C6" s="0"/>
+      <ns0:c r="D6" s="0"/>
+      <ns0:c r="E6" s="0"/>
+      <ns0:c r="F6" s="0"/>
+      <ns0:c r="G6" s="0"/>
+      <ns0:c r="H6" s="0"/>
+      <ns0:c r="I6" s="0"/>
+      <ns0:c r="J6" s="0"/>
+      <ns0:c r="K6" s="0"/>
+      <ns0:c r="L6" s="0"/>
+      <ns0:c r="M6" s="0"/>
+      <ns0:c r="N6" s="0"/>
+      <ns0:c r="O6" s="0"/>
+      <ns0:c r="P6" s="0"/>
+    </ns0:row>
+    <ns0:row r="7" spans="1:16">
+      <ns0:c r="A7" s="3"/>
+      <ns0:c r="B7" s="4" t="str">
+        <ns0:v>CircleShape</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="5" t="str">
+        <ns0:v>Shape</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="5"/>
+      <ns0:c r="E7" s="5"/>
+      <ns0:c r="F7" s="5" t="str">
+        <ns0:v>圆形</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="5"/>
+      <ns0:c r="H7" s="5"/>
+      <ns0:c r="I7" s="5"/>
+      <ns0:c r="J7" s="5" t="str">
+        <ns0:v>radius</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" s="5"/>
+      <ns0:c r="L7" s="5" t="str">
+        <ns0:v>float</ns0:v>
+      </ns0:c>
+      <ns0:c r="M7" s="5"/>
+      <ns0:c r="N7" s="5" t="str">
+        <ns0:v>圆形半径</ns0:v>
+      </ns0:c>
+      <ns0:c r="O7" s="5"/>
+      <ns0:c r="P7" s="25"/>
+    </ns0:row>
+    <ns0:row r="8" spans="1:16">
+      <ns0:c r="A8" s="0"/>
+      <ns0:c r="B8" s="0"/>
+      <ns0:c r="C8" s="0"/>
+      <ns0:c r="D8" s="0"/>
+      <ns0:c r="E8" s="0"/>
+      <ns0:c r="F8" s="0"/>
+      <ns0:c r="G8" s="0"/>
+      <ns0:c r="H8" s="0"/>
+      <ns0:c r="I8" s="0"/>
+      <ns0:c r="J8" s="0"/>
+      <ns0:c r="K8" s="0"/>
+      <ns0:c r="L8" s="0"/>
+      <ns0:c r="M8" s="0"/>
+      <ns0:c r="N8" s="0"/>
+      <ns0:c r="O8" s="0"/>
+      <ns0:c r="P8" s="0"/>
+    </ns0:row>
+    <ns0:row r="9" spans="1:16">
+      <ns0:c r="A9" s="3"/>
+      <ns0:c r="B9" s="6" t="str">
+        <ns0:v>RectangleShape</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="7" t="str">
+        <ns0:v>Shape</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="7"/>
+      <ns0:c r="E9" s="7"/>
+      <ns0:c r="F9" s="7" t="str">
+        <ns0:v>矩形</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="7"/>
+      <ns0:c r="H9" s="7"/>
+      <ns0:c r="I9" s="7"/>
+      <ns0:c r="J9" s="7" t="str">
+        <ns0:v>rect</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9" s="7"/>
+      <ns0:c r="L9" s="7" t="str">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="M9" s="7"/>
+      <ns0:c r="N9" s="7" t="str">
+        <ns0:v>矩形长宽</ns0:v>
+      </ns0:c>
+      <ns0:c r="O9" s="7"/>
+      <ns0:c r="P9" s="26"/>
+    </ns0:row>
+    <ns0:row r="10" spans="1:16">
+      <ns0:c r="A10" s="3"/>
+      <ns0:c r="B10" s="8"/>
+      <ns0:c r="C10" s="9"/>
+      <ns0:c r="D10" s="9"/>
+      <ns0:c r="E10" s="9"/>
+      <ns0:c r="F10" s="9"/>
+      <ns0:c r="G10" s="9"/>
+      <ns0:c r="H10" s="9"/>
+      <ns0:c r="I10" s="9"/>
+      <ns0:c r="J10" s="9" t="str">
+        <ns0:v>pivot</ns0:v>
+      </ns0:c>
+      <ns0:c r="K10" s="9"/>
+      <ns0:c r="L10" s="9" t="str">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="M10" s="9"/>
+      <ns0:c r="N10" s="9" t="str">
+        <ns0:v>矩形定位点</ns0:v>
+      </ns0:c>
+      <ns0:c r="O10" s="9"/>
+      <ns0:c r="P10" s="27"/>
+    </ns0:row>
+    <ns0:row r="11" spans="1:16">
+      <ns0:c r="A11" s="0"/>
+      <ns0:c r="B11" s="0"/>
+      <ns0:c r="C11" s="0"/>
+      <ns0:c r="D11" s="0"/>
+      <ns0:c r="E11" s="0"/>
+      <ns0:c r="F11" s="0"/>
+      <ns0:c r="G11" s="0"/>
+      <ns0:c r="H11" s="0"/>
+      <ns0:c r="I11" s="0"/>
+      <ns0:c r="J11" s="0"/>
+      <ns0:c r="K11" s="0"/>
+      <ns0:c r="L11" s="0"/>
+      <ns0:c r="M11" s="0"/>
+      <ns0:c r="N11" s="0"/>
+      <ns0:c r="O11" s="0"/>
+      <ns0:c r="P11" s="0"/>
+    </ns0:row>
+    <ns0:row r="12" spans="2:16">
+      <ns0:c r="B12" s="10" t="str">
+        <ns0:v>bean.FunctionOpenCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" s="11"/>
+      <ns0:c r="D12" s="11"/>
+      <ns0:c r="E12" s="11"/>
+      <ns0:c r="F12" s="11" t="str">
+        <ns0:v>功能开启条件基类</ns0:v>
+      </ns0:c>
+      <ns0:c r="G12" s="11"/>
+      <ns0:c r="H12" s="11"/>
+      <ns0:c r="I12" s="11"/>
+      <ns0:c r="J12" s="11"/>
+      <ns0:c r="K12" s="11"/>
+      <ns0:c r="L12" s="11"/>
+      <ns0:c r="M12" s="11"/>
+      <ns0:c r="N12" s="11"/>
+      <ns0:c r="O12" s="11"/>
+      <ns0:c r="P12" s="28"/>
+    </ns0:row>
+    <ns0:row r="14" spans="2:16">
+      <ns0:c r="B14" s="12" t="str">
+        <ns0:v>PlayerLevelCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" s="13" t="str">
+        <ns0:v>bean.FunctionOpenCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" s="11"/>
+      <ns0:c r="E14" s="11"/>
+      <ns0:c r="F14" s="11" t="str">
+        <ns0:v>玩家等级</ns0:v>
+      </ns0:c>
+      <ns0:c r="G14" s="11"/>
+      <ns0:c r="H14" s="11"/>
+      <ns0:c r="I14" s="11"/>
+      <ns0:c r="J14" s="11" t="str">
+        <ns0:v>level</ns0:v>
+      </ns0:c>
+      <ns0:c r="K14" s="11"/>
+      <ns0:c r="L14" s="11" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M14" s="11"/>
+      <ns0:c r="N14" s="11" t="str">
+        <ns0:v>玩家等级</ns0:v>
+      </ns0:c>
+      <ns0:c r="O14" s="11"/>
+      <ns0:c r="P14" s="28"/>
+    </ns0:row>
+    <ns0:row r="16" spans="2:16">
+      <ns0:c r="B16" s="12" t="str">
+        <ns0:v>MissionProgressCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="C16" s="13" t="str">
+        <ns0:v>bean.FunctionOpenCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" s="11"/>
+      <ns0:c r="E16" s="11"/>
+      <ns0:c r="F16" s="11" t="str">
+        <ns0:v>主线关卡进度</ns0:v>
+      </ns0:c>
+      <ns0:c r="G16" s="11"/>
+      <ns0:c r="H16" s="11"/>
+      <ns0:c r="I16" s="11"/>
+      <ns0:c r="J16" s="11" t="str">
+        <ns0:v>missionIndex</ns0:v>
+      </ns0:c>
+      <ns0:c r="K16" s="11"/>
+      <ns0:c r="L16" s="11" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M16" s="11"/>
+      <ns0:c r="N16" s="11" t="str">
+        <ns0:v>主线任务进度</ns0:v>
+      </ns0:c>
+      <ns0:c r="O16" s="11"/>
+      <ns0:c r="P16" s="28"/>
+    </ns0:row>
+    <ns0:row r="18" spans="2:16">
+      <ns0:c r="B18" s="12" t="str">
+        <ns0:v>DisabledCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="C18" s="13" t="str">
+        <ns0:v>bean.FunctionOpenCondition</ns0:v>
+      </ns0:c>
+      <ns0:c r="D18" s="11"/>
+      <ns0:c r="E18" s="11"/>
+      <ns0:c r="F18" s="11" t="str">
+        <ns0:v>暂未开放</ns0:v>
+      </ns0:c>
+      <ns0:c r="G18" s="11" t="str">
+        <ns0:v>始终不满足，无参数</ns0:v>
+      </ns0:c>
+      <ns0:c r="H18" s="11"/>
+      <ns0:c r="I18" s="11"/>
+      <ns0:c r="J18" s="11"/>
+      <ns0:c r="K18" s="11"/>
+      <ns0:c r="L18" s="11"/>
+      <ns0:c r="M18" s="11"/>
+      <ns0:c r="N18" s="11"/>
+      <ns0:c r="O18" s="11"/>
+      <ns0:c r="P18" s="28"/>
+    </ns0:row>
+    <ns0:row r="20" spans="1:16">
+      <ns0:c r="A20" s="14"/>
+      <ns0:c r="B20" s="15" t="str">
+        <ns0:v>bean.BattleSceneCellCoord</ns0:v>
+      </ns0:c>
+      <ns0:c r="C20" s="16"/>
+      <ns0:c r="D20" s="16"/>
+      <ns0:c r="E20" s="16"/>
+      <ns0:c r="F20" s="16" t="str">
+        <ns0:v>场景格子坐标</ns0:v>
+      </ns0:c>
+      <ns0:c r="G20" s="16"/>
+      <ns0:c r="H20" s="16"/>
+      <ns0:c r="I20" s="16"/>
+      <ns0:c r="J20" s="16" t="str">
+        <ns0:v>q</ns0:v>
+      </ns0:c>
+      <ns0:c r="K20" s="16" t="str">
+        <ns0:v>列坐标</ns0:v>
+      </ns0:c>
+      <ns0:c r="L20" s="16" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M20" s="16"/>
+      <ns0:c r="N20" s="16" t="str">
+        <ns0:v>标准六边形列坐标</ns0:v>
+      </ns0:c>
+      <ns0:c r="O20" s="16"/>
+      <ns0:c r="P20" s="29"/>
+    </ns0:row>
+    <ns0:row r="21" spans="1:16">
+      <ns0:c r="A21" s="17"/>
+      <ns0:c r="B21" s="18"/>
+      <ns0:c r="C21" s="19"/>
+      <ns0:c r="D21" s="19"/>
+      <ns0:c r="E21" s="19"/>
+      <ns0:c r="F21" s="19"/>
+      <ns0:c r="G21" s="19"/>
+      <ns0:c r="H21" s="19"/>
+      <ns0:c r="I21" s="19"/>
+      <ns0:c r="J21" s="19" t="str">
+        <ns0:v>k</ns0:v>
+      </ns0:c>
+      <ns0:c r="K21" s="19" t="str">
+        <ns0:v>行坐标</ns0:v>
+      </ns0:c>
+      <ns0:c r="L21" s="19" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M21" s="19"/>
+      <ns0:c r="N21" s="19" t="str">
+        <ns0:v>k-q须为偶数</ns0:v>
+      </ns0:c>
+      <ns0:c r="O21" s="19"/>
+      <ns0:c r="P21" s="30"/>
+    </ns0:row>
+    <ns0:row r="22" spans="1:16">
+      <ns0:c r="A22" s="20"/>
+      <ns0:c r="B22" s="20"/>
+      <ns0:c r="C22" s="20"/>
+      <ns0:c r="D22" s="20"/>
+      <ns0:c r="E22" s="20"/>
+      <ns0:c r="F22" s="20"/>
+      <ns0:c r="G22" s="20"/>
+      <ns0:c r="H22" s="20"/>
+      <ns0:c r="I22" s="20"/>
+      <ns0:c r="J22" s="20"/>
+      <ns0:c r="K22" s="20"/>
+      <ns0:c r="L22" s="20"/>
+      <ns0:c r="M22" s="20"/>
+      <ns0:c r="N22" s="20"/>
+      <ns0:c r="O22" s="20"/>
+      <ns0:c r="P22" s="20"/>
+    </ns0:row>
+    <ns0:row r="23" spans="1:16">
+      <ns0:c r="A23" s="14"/>
+      <ns0:c r="B23" s="15" t="str">
+        <ns0:v>bean.BattleSceneAppearance</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" s="16"/>
+      <ns0:c r="D23" s="16"/>
+      <ns0:c r="E23" s="16"/>
+      <ns0:c r="F23" s="16" t="str">
+        <ns0:v>场景外观</ns0:v>
+      </ns0:c>
+      <ns0:c r="G23" s="16"/>
+      <ns0:c r="H23" s="16"/>
+      <ns0:c r="I23" s="16"/>
+      <ns0:c r="J23" s="16" t="str">
+        <ns0:v>resourceType</ns0:v>
+      </ns0:c>
+      <ns0:c r="K23" s="16" t="str">
+        <ns0:v>资源类型</ns0:v>
+      </ns0:c>
+      <ns0:c r="L23" s="16" t="str">
+        <ns0:v>BattleSceneResourceType</ns0:v>
+      </ns0:c>
+      <ns0:c r="M23" s="16"/>
+      <ns0:c r="N23" s="16" t="str">
+        <ns0:v>静态图片或帧动画</ns0:v>
+      </ns0:c>
+      <ns0:c r="O23" s="16"/>
+      <ns0:c r="P23" s="29"/>
+    </ns0:row>
+    <ns0:row r="24" spans="1:16">
+      <ns0:c r="A24" s="21"/>
+      <ns0:c r="B24" s="22"/>
+      <ns0:c r="C24" s="23"/>
+      <ns0:c r="D24" s="23"/>
+      <ns0:c r="E24" s="23"/>
+      <ns0:c r="F24" s="23"/>
+      <ns0:c r="G24" s="23"/>
+      <ns0:c r="H24" s="23"/>
+      <ns0:c r="I24" s="23"/>
+      <ns0:c r="J24" s="23" t="str">
+        <ns0:v>resource</ns0:v>
+      </ns0:c>
+      <ns0:c r="K24" s="23" t="str">
+        <ns0:v>资源引用</ns0:v>
+      </ns0:c>
+      <ns0:c r="L24" s="23" t="str">
+        <ns0:v>string</ns0:v>
+      </ns0:c>
+      <ns0:c r="M24" s="23"/>
+      <ns0:c r="N24" s="23" t="str">
+        <ns0:v>资源逻辑引用；仅用于显示</ns0:v>
+      </ns0:c>
+      <ns0:c r="O24" s="23"/>
+      <ns0:c r="P24" s="31"/>
+    </ns0:row>
+    <ns0:row r="25" spans="1:16">
+      <ns0:c r="A25" s="21"/>
+      <ns0:c r="B25" s="22"/>
+      <ns0:c r="C25" s="23"/>
+      <ns0:c r="D25" s="23"/>
+      <ns0:c r="E25" s="23"/>
+      <ns0:c r="F25" s="23"/>
+      <ns0:c r="G25" s="23"/>
+      <ns0:c r="H25" s="23"/>
+      <ns0:c r="I25" s="23"/>
+      <ns0:c r="J25" s="23" t="str">
+        <ns0:v>layer</ns0:v>
+      </ns0:c>
+      <ns0:c r="K25" s="23" t="str">
+        <ns0:v>表现层</ns0:v>
+      </ns0:c>
+      <ns0:c r="L25" s="23" t="str">
+        <ns0:v>BattleSceneVisualLayer</ns0:v>
+      </ns0:c>
+      <ns0:c r="M25" s="23"/>
+      <ns0:c r="N25" s="23" t="str">
+        <ns0:v>只决定表现层级</ns0:v>
+      </ns0:c>
+      <ns0:c r="O25" s="23"/>
+      <ns0:c r="P25" s="31"/>
+    </ns0:row>
+    <ns0:row r="26" spans="1:16">
+      <ns0:c r="A26" s="21"/>
+      <ns0:c r="B26" s="22"/>
+      <ns0:c r="C26" s="23"/>
+      <ns0:c r="D26" s="23"/>
+      <ns0:c r="E26" s="23"/>
+      <ns0:c r="F26" s="23"/>
+      <ns0:c r="G26" s="23"/>
+      <ns0:c r="H26" s="23"/>
+      <ns0:c r="I26" s="23"/>
+      <ns0:c r="J26" s="23" t="str">
+        <ns0:v>cells</ns0:v>
+      </ns0:c>
+      <ns0:c r="K26" s="23" t="str">
+        <ns0:v>关联格子</ns0:v>
+      </ns0:c>
+      <ns0:c r="L26" s="23" t="str">
+        <ns0:v>list,bean.BattleSceneCellCoord</ns0:v>
+      </ns0:c>
+      <ns0:c r="M26" s="23"/>
+      <ns0:c r="N26" s="23" t="str">
+        <ns0:v>现有格子的绝对q/k坐标；不改变玩法占格</ns0:v>
+      </ns0:c>
+      <ns0:c r="O26" s="23"/>
+      <ns0:c r="P26" s="31"/>
+    </ns0:row>
+    <ns0:row r="27" spans="1:16">
+      <ns0:c r="A27" s="21"/>
+      <ns0:c r="B27" s="22"/>
+      <ns0:c r="C27" s="23"/>
+      <ns0:c r="D27" s="23"/>
+      <ns0:c r="E27" s="23"/>
+      <ns0:c r="F27" s="23"/>
+      <ns0:c r="G27" s="23"/>
+      <ns0:c r="H27" s="23"/>
+      <ns0:c r="I27" s="23"/>
+      <ns0:c r="J27" s="23" t="str">
+        <ns0:v>anchor</ns0:v>
+      </ns0:c>
+      <ns0:c r="K27" s="23" t="str">
+        <ns0:v>锚点格子</ns0:v>
+      </ns0:c>
+      <ns0:c r="L27" s="23" t="str">
+        <ns0:v>bean.BattleSceneCellCoord</ns0:v>
+      </ns0:c>
+      <ns0:c r="M27" s="23"/>
+      <ns0:c r="N27" s="23" t="str">
+        <ns0:v>资源pivot对齐该格子中心后叠加offset</ns0:v>
+      </ns0:c>
+      <ns0:c r="O27" s="23"/>
+      <ns0:c r="P27" s="31"/>
+    </ns0:row>
+    <ns0:row r="28" spans="1:16">
+      <ns0:c r="A28" s="17"/>
+      <ns0:c r="B28" s="18"/>
+      <ns0:c r="C28" s="19"/>
+      <ns0:c r="D28" s="19"/>
+      <ns0:c r="E28" s="19"/>
+      <ns0:c r="F28" s="19"/>
+      <ns0:c r="G28" s="19"/>
+      <ns0:c r="H28" s="19"/>
+      <ns0:c r="I28" s="19"/>
+      <ns0:c r="J28" s="19" t="str">
+        <ns0:v>offset</ns0:v>
+      </ns0:c>
+      <ns0:c r="K28" s="19" t="str">
+        <ns0:v>显示偏移</ns0:v>
+      </ns0:c>
+      <ns0:c r="L28" s="19" t="str">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="M28" s="19"/>
+      <ns0:c r="N28" s="19" t="str">
+        <ns0:v>设计像素，X右Y下；不改变逻辑坐标</ns0:v>
+      </ns0:c>
+      <ns0:c r="O28" s="19"/>
+      <ns0:c r="P28" s="30"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="30">
+      <ns0:c r="A30" s="32"/>
+      <ns0:c r="B30" s="33" t="str">
+        <ns0:v>bean.CardContent</ns0:v>
+      </ns0:c>
+      <ns0:c r="C30" s="34"/>
+      <ns0:c r="D30" s="35"/>
+      <ns0:c r="E30" s="36"/>
+      <ns0:c r="F30" s="37" t="str">
+        <ns0:v>卡牌内容</ns0:v>
+      </ns0:c>
+      <ns0:c r="G30" s="38"/>
+      <ns0:c r="H30" s="39"/>
+      <ns0:c r="I30" s="40"/>
+      <ns0:c r="J30" s="41"/>
+      <ns0:c r="K30" s="42"/>
+      <ns0:c r="L30" s="43"/>
+      <ns0:c r="M30" s="44"/>
+      <ns0:c r="N30" s="45"/>
+      <ns0:c r="O30" s="46"/>
+      <ns0:c r="P30" s="47"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="32">
+      <ns0:c r="A32" s="48"/>
+      <ns0:c r="B32" s="49" t="str">
+        <ns0:v>UnitCardContent</ns0:v>
+      </ns0:c>
+      <ns0:c r="C32" s="50" t="str">
+        <ns0:v>bean.CardContent</ns0:v>
+      </ns0:c>
+      <ns0:c r="D32" s="51"/>
+      <ns0:c r="E32" s="52"/>
+      <ns0:c r="F32" s="53" t="str">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="G32" s="54"/>
+      <ns0:c r="H32" s="55"/>
+      <ns0:c r="I32" s="56"/>
+      <ns0:c r="J32" s="57" t="str">
+        <ns0:v>unitId</ns0:v>
+      </ns0:c>
+      <ns0:c r="K32" s="58" t="str">
+        <ns0:v>兵种ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="L32" s="59" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M32" s="60"/>
+      <ns0:c r="N32" s="61" t="str">
+        <ns0:v>引用UnitResource.id；经生产配置关联生产建筑</ns0:v>
+      </ns0:c>
+      <ns0:c r="O32" s="62"/>
+      <ns0:c r="P32" s="63"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="34">
+      <ns0:c r="A34" s="64"/>
+      <ns0:c r="B34" s="65" t="str">
+        <ns0:v>BuildingCardContent</ns0:v>
+      </ns0:c>
+      <ns0:c r="C34" s="66" t="str">
+        <ns0:v>bean.CardContent</ns0:v>
+      </ns0:c>
+      <ns0:c r="D34" s="67"/>
+      <ns0:c r="E34" s="68"/>
+      <ns0:c r="F34" s="69" t="str">
+        <ns0:v>建筑卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="G34" s="70"/>
+      <ns0:c r="H34" s="71"/>
+      <ns0:c r="I34" s="72"/>
+      <ns0:c r="J34" s="73" t="str">
+        <ns0:v>buildingId</ns0:v>
+      </ns0:c>
+      <ns0:c r="K34" s="74" t="str">
+        <ns0:v>建筑ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="L34" s="75" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M34" s="76"/>
+      <ns0:c r="N34" s="77" t="str">
+        <ns0:v>引用BuildingResource.id；不配置基地或重复生产建筑卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="O34" s="78"/>
+      <ns0:c r="P34" s="79"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="36">
+      <ns0:c r="A36" s="80"/>
+      <ns0:c r="B36" s="81" t="str">
+        <ns0:v>bean.BuildingAppearance</ns0:v>
+      </ns0:c>
+      <ns0:c r="C36" s="82"/>
+      <ns0:c r="D36" s="83"/>
+      <ns0:c r="E36" s="84"/>
+      <ns0:c r="F36" s="85" t="str">
+        <ns0:v>建筑外观</ns0:v>
+      </ns0:c>
+      <ns0:c r="G36" s="86"/>
+      <ns0:c r="H36" s="87"/>
+      <ns0:c r="I36" s="88"/>
+      <ns0:c r="J36" s="89" t="str">
+        <ns0:v>direction</ns0:v>
+      </ns0:c>
+      <ns0:c r="K36" s="90" t="str">
+        <ns0:v>朝向</ns0:v>
+      </ns0:c>
+      <ns0:c r="L36" s="91" t="str">
+        <ns0:v>BuildingAppearanceDirection</ns0:v>
+      </ns0:c>
+      <ns0:c r="M36" s="92"/>
+      <ns0:c r="N36" s="93" t="str">
+        <ns0:v>固定或上下朝向；不表示敌我阵营</ns0:v>
+      </ns0:c>
+      <ns0:c r="O36" s="94"/>
+      <ns0:c r="P36" s="95"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="37">
+      <ns0:c r="A37" s="96"/>
+      <ns0:c r="B37" s="97"/>
+      <ns0:c r="C37" s="98"/>
+      <ns0:c r="D37" s="99"/>
+      <ns0:c r="E37" s="100"/>
+      <ns0:c r="F37" s="101"/>
+      <ns0:c r="G37" s="102"/>
+      <ns0:c r="H37" s="103"/>
+      <ns0:c r="I37" s="104"/>
+      <ns0:c r="J37" s="105" t="str">
+        <ns0:v>part</ns0:v>
+      </ns0:c>
+      <ns0:c r="K37" s="106" t="str">
+        <ns0:v>外观部件</ns0:v>
+      </ns0:c>
+      <ns0:c r="L37" s="107" t="str">
+        <ns0:v>BuildingAppearancePart</ns0:v>
+      </ns0:c>
+      <ns0:c r="M37" s="108"/>
+      <ns0:c r="N37" s="109" t="str">
+        <ns0:v>主体、底座、炮身或独立地面阴影</ns0:v>
+      </ns0:c>
+      <ns0:c r="O37" s="110"/>
+      <ns0:c r="P37" s="111"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="38">
+      <ns0:c r="A38" s="112"/>
+      <ns0:c r="B38" s="113"/>
+      <ns0:c r="C38" s="114"/>
+      <ns0:c r="D38" s="115"/>
+      <ns0:c r="E38" s="116"/>
+      <ns0:c r="F38" s="117"/>
+      <ns0:c r="G38" s="118"/>
+      <ns0:c r="H38" s="119"/>
+      <ns0:c r="I38" s="120"/>
+      <ns0:c r="J38" s="121" t="str">
+        <ns0:v>resourceType</ns0:v>
+      </ns0:c>
+      <ns0:c r="K38" s="122" t="str">
+        <ns0:v>资源类型</ns0:v>
+      </ns0:c>
+      <ns0:c r="L38" s="123" t="str">
+        <ns0:v>BattleSceneResourceType</ns0:v>
+      </ns0:c>
+      <ns0:c r="M38" s="124"/>
+      <ns0:c r="N38" s="125" t="str">
+        <ns0:v>复用静态图片与帧动画资源类型</ns0:v>
+      </ns0:c>
+      <ns0:c r="O38" s="126"/>
+      <ns0:c r="P38" s="127"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="39">
+      <ns0:c r="A39" s="128"/>
+      <ns0:c r="B39" s="129"/>
+      <ns0:c r="C39" s="130"/>
+      <ns0:c r="D39" s="131"/>
+      <ns0:c r="E39" s="132"/>
+      <ns0:c r="F39" s="133"/>
+      <ns0:c r="G39" s="134"/>
+      <ns0:c r="H39" s="135"/>
+      <ns0:c r="I39" s="136"/>
+      <ns0:c r="J39" s="137" t="str">
+        <ns0:v>resource</ns0:v>
+      </ns0:c>
+      <ns0:c r="K39" s="138" t="str">
+        <ns0:v>资源引用</ns0:v>
+      </ns0:c>
+      <ns0:c r="L39" s="139" t="str">
+        <ns0:v>string</ns0:v>
+      </ns0:c>
+      <ns0:c r="M39" s="140"/>
+      <ns0:c r="N39" s="141" t="str">
+        <ns0:v>相对Assets/Art/unpack/；不填固定后缀</ns0:v>
+      </ns0:c>
+      <ns0:c r="O39" s="142"/>
+      <ns0:c r="P39" s="143"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="40">
+      <ns0:c r="A40" s="144"/>
+      <ns0:c r="B40" s="145"/>
+      <ns0:c r="C40" s="146"/>
+      <ns0:c r="D40" s="147"/>
+      <ns0:c r="E40" s="148"/>
+      <ns0:c r="F40" s="149"/>
+      <ns0:c r="G40" s="150"/>
+      <ns0:c r="H40" s="151"/>
+      <ns0:c r="I40" s="152"/>
+      <ns0:c r="J40" s="153" t="str">
+        <ns0:v>offset</ns0:v>
+      </ns0:c>
+      <ns0:c r="K40" s="154" t="str">
+        <ns0:v>显示偏移</ns0:v>
+      </ns0:c>
+      <ns0:c r="L40" s="155" t="str">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="M40" s="156"/>
+      <ns0:c r="N40" s="157" t="str">
+        <ns0:v>相对建筑定位锚点；设计像素，X右Y下</ns0:v>
+      </ns0:c>
+      <ns0:c r="O40" s="158"/>
+      <ns0:c r="P40" s="159"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="42">
+      <ns0:c r="A42" s="160"/>
+      <ns0:c r="B42" s="161" t="str">
+        <ns0:v>bean.UnitAppearance</ns0:v>
+      </ns0:c>
+      <ns0:c r="C42" s="162"/>
+      <ns0:c r="D42" s="163"/>
+      <ns0:c r="E42" s="164"/>
+      <ns0:c r="F42" s="165" t="str">
+        <ns0:v>兵种外观</ns0:v>
+      </ns0:c>
+      <ns0:c r="G42" s="166"/>
+      <ns0:c r="H42" s="167"/>
+      <ns0:c r="I42" s="168"/>
+      <ns0:c r="J42" s="169" t="str">
+        <ns0:v>action</ns0:v>
+      </ns0:c>
+      <ns0:c r="K42" s="170" t="str">
+        <ns0:v>动作</ns0:v>
+      </ns0:c>
+      <ns0:c r="L42" s="171" t="str">
+        <ns0:v>UnitActionType</ns0:v>
+      </ns0:c>
+      <ns0:c r="M42" s="172"/>
+      <ns0:c r="N42" s="173" t="str">
+        <ns0:v>移动、死亡、攻击动作1；后续按技能扩展</ns0:v>
+      </ns0:c>
+      <ns0:c r="O42" s="174"/>
+      <ns0:c r="P42" s="175"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="43">
+      <ns0:c r="A43" s="176"/>
+      <ns0:c r="B43" s="177"/>
+      <ns0:c r="C43" s="178"/>
+      <ns0:c r="D43" s="179"/>
+      <ns0:c r="E43" s="180"/>
+      <ns0:c r="F43" s="181"/>
+      <ns0:c r="G43" s="182"/>
+      <ns0:c r="H43" s="183"/>
+      <ns0:c r="I43" s="184"/>
+      <ns0:c r="J43" s="185" t="str">
+        <ns0:v>direction</ns0:v>
+      </ns0:c>
+      <ns0:c r="K43" s="186" t="str">
+        <ns0:v>源朝向</ns0:v>
+      </ns0:c>
+      <ns0:c r="L43" s="187" t="str">
+        <ns0:v>UnitAppearanceDirection</ns0:v>
+      </ns0:c>
+      <ns0:c r="M43" s="188"/>
+      <ns0:c r="N43" s="189" t="str">
+        <ns0:v>仅配五个源朝向；左侧由右侧水平镜像</ns0:v>
+      </ns0:c>
+      <ns0:c r="O43" s="190"/>
+      <ns0:c r="P43" s="191"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="44">
+      <ns0:c r="A44" s="192"/>
+      <ns0:c r="B44" s="193"/>
+      <ns0:c r="C44" s="194"/>
+      <ns0:c r="D44" s="195"/>
+      <ns0:c r="E44" s="196"/>
+      <ns0:c r="F44" s="197"/>
+      <ns0:c r="G44" s="198"/>
+      <ns0:c r="H44" s="199"/>
+      <ns0:c r="I44" s="200"/>
+      <ns0:c r="J44" s="201" t="str">
+        <ns0:v>resource</ns0:v>
+      </ns0:c>
+      <ns0:c r="K44" s="202" t="str">
+        <ns0:v>动画资源</ns0:v>
+      </ns0:c>
+      <ns0:c r="L44" s="203" t="str">
+        <ns0:v>string</ns0:v>
+      </ns0:c>
+      <ns0:c r="M44" s="204"/>
+      <ns0:c r="N44" s="205" t="str">
+        <ns0:v>相对Assets/Art/frameAnimation/的动画资源标识</ns0:v>
+      </ns0:c>
+      <ns0:c r="O44" s="206"/>
+      <ns0:c r="P44" s="207"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="45">
+      <ns0:c r="A45" s="208"/>
+      <ns0:c r="B45" s="209"/>
+      <ns0:c r="C45" s="210"/>
+      <ns0:c r="D45" s="211"/>
+      <ns0:c r="E45" s="212"/>
+      <ns0:c r="F45" s="213"/>
+      <ns0:c r="G45" s="214"/>
+      <ns0:c r="H45" s="215"/>
+      <ns0:c r="I45" s="216"/>
+      <ns0:c r="J45" s="217" t="str">
+        <ns0:v>loop</ns0:v>
+      </ns0:c>
+      <ns0:c r="K45" s="218" t="str">
+        <ns0:v>循环播放</ns0:v>
+      </ns0:c>
+      <ns0:c r="L45" s="219" t="str">
+        <ns0:v>bool</ns0:v>
+      </ns0:c>
+      <ns0:c r="M45" s="220"/>
+      <ns0:c r="N45" s="221" t="str">
+        <ns0:v>移动循环；其他动作分别确定播放方式</ns0:v>
+      </ns0:c>
+      <ns0:c r="O45" s="222"/>
+      <ns0:c r="P45" s="223"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="46">
+      <ns0:c r="A46" s="224"/>
+      <ns0:c r="B46" s="225"/>
+      <ns0:c r="C46" s="226"/>
+      <ns0:c r="D46" s="227"/>
+      <ns0:c r="E46" s="228"/>
+      <ns0:c r="F46" s="229"/>
+      <ns0:c r="G46" s="230"/>
+      <ns0:c r="H46" s="231"/>
+      <ns0:c r="I46" s="232"/>
+      <ns0:c r="J46" s="233" t="str">
+        <ns0:v>offset</ns0:v>
+      </ns0:c>
+      <ns0:c r="K46" s="234" t="str">
+        <ns0:v>显示偏移</ns0:v>
+      </ns0:c>
+      <ns0:c r="L46" s="235" t="str">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="M46" s="236"/>
+      <ns0:c r="N46" s="237" t="str">
+        <ns0:v>相对地面定位点；设计像素，X右Y下</ns0:v>
+      </ns0:c>
+      <ns0:c r="O46" s="238"/>
+      <ns0:c r="P46" s="239"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="48">
+      <ns0:c r="A48" s="240"/>
+      <ns0:c r="B48" s="241" t="str">
+        <ns0:v>bean.ItemCost</ns0:v>
+      </ns0:c>
+      <ns0:c r="C48" s="242"/>
+      <ns0:c r="D48" s="243"/>
+      <ns0:c r="E48" s="244"/>
+      <ns0:c r="F48" s="245" t="str">
+        <ns0:v>道具消耗</ns0:v>
+      </ns0:c>
+      <ns0:c r="G48" s="246"/>
+      <ns0:c r="H48" s="247"/>
+      <ns0:c r="I48" s="248"/>
+      <ns0:c r="J48" s="249" t="str">
+        <ns0:v>itemId</ns0:v>
+      </ns0:c>
+      <ns0:c r="K48" s="250" t="str">
+        <ns0:v>道具ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="L48" s="251" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M48" s="252"/>
+      <ns0:c r="N48" s="253" t="str">
+        <ns0:v>引用ItemResource.id；碎片或指定局外货币</ns0:v>
+      </ns0:c>
+      <ns0:c r="O48" s="254"/>
+      <ns0:c r="P48" s="255"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="49">
+      <ns0:c r="A49" s="256"/>
+      <ns0:c r="B49" s="257"/>
+      <ns0:c r="C49" s="258"/>
+      <ns0:c r="D49" s="259"/>
+      <ns0:c r="E49" s="260"/>
+      <ns0:c r="F49" s="261"/>
+      <ns0:c r="G49" s="262"/>
+      <ns0:c r="H49" s="263"/>
+      <ns0:c r="I49" s="264"/>
+      <ns0:c r="J49" s="265" t="str">
+        <ns0:v>count</ns0:v>
+      </ns0:c>
+      <ns0:c r="K49" s="266" t="str">
+        <ns0:v>消耗数量</ns0:v>
+      </ns0:c>
+      <ns0:c r="L49" s="267" t="str">
+        <ns0:v>double</ns0:v>
+      </ns0:c>
+      <ns0:c r="M49" s="268"/>
+      <ns0:c r="N49" s="269" t="str">
+        <ns0:v>有限正数；碎片须为整数，不含局内货币</ns0:v>
+      </ns0:c>
+      <ns0:c r="O49" s="270"/>
+      <ns0:c r="P49" s="271"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="51">
+      <ns0:c r="A51" s="272"/>
+      <ns0:c r="B51" s="273" t="str">
+        <ns0:v>bean.BattleDeckCard</ns0:v>
+      </ns0:c>
+      <ns0:c r="C51" s="274"/>
+      <ns0:c r="D51" s="275"/>
+      <ns0:c r="E51" s="276"/>
+      <ns0:c r="F51" s="277" t="str">
+        <ns0:v>卡组卡牌</ns0:v>
+      </ns0:c>
+      <ns0:c r="G51" s="278"/>
+      <ns0:c r="H51" s="279"/>
+      <ns0:c r="I51" s="280"/>
+      <ns0:c r="J51" s="281" t="str">
+        <ns0:v>cardId</ns0:v>
+      </ns0:c>
+      <ns0:c r="K51" s="282" t="str">
+        <ns0:v>卡牌ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="L51" s="283" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M51" s="284"/>
+      <ns0:c r="N51" s="285" t="str">
+        <ns0:v>引用CardResource.id；卡组内不得重复</ns0:v>
+      </ns0:c>
+      <ns0:c r="O51" s="286"/>
+      <ns0:c r="P51" s="287"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="52">
+      <ns0:c r="A52" s="288"/>
+      <ns0:c r="B52" s="289"/>
+      <ns0:c r="C52" s="290"/>
+      <ns0:c r="D52" s="291"/>
+      <ns0:c r="E52" s="292"/>
+      <ns0:c r="F52" s="293"/>
+      <ns0:c r="G52" s="294"/>
+      <ns0:c r="H52" s="295"/>
+      <ns0:c r="I52" s="296"/>
+      <ns0:c r="J52" s="297" t="str">
+        <ns0:v>locked</ns0:v>
+      </ns0:c>
+      <ns0:c r="K52" s="298" t="str">
+        <ns0:v>固定槽位</ns0:v>
+      </ns0:c>
+      <ns0:c r="L52" s="299" t="str">
+        <ns0:v>bool</ns0:v>
+      </ns0:c>
+      <ns0:c r="M52" s="300"/>
+      <ns0:c r="N52" s="301" t="str">
+        <ns0:v>不可移除替换，仍占槽位</ns0:v>
+      </ns0:c>
+      <ns0:c r="O52" s="302"/>
+      <ns0:c r="P52" s="303"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="54">
+      <ns0:c r="A54" s="304"/>
+      <ns0:c r="B54" s="305" t="str">
+        <ns0:v>bean.UnitQualityWeight</ns0:v>
+      </ns0:c>
+      <ns0:c r="C54" s="306"/>
+      <ns0:c r="D54" s="307"/>
+      <ns0:c r="E54" s="308"/>
+      <ns0:c r="F54" s="309" t="str">
+        <ns0:v>兵种品质权重</ns0:v>
+      </ns0:c>
+      <ns0:c r="G54" s="310"/>
+      <ns0:c r="H54" s="311"/>
+      <ns0:c r="I54" s="312"/>
+      <ns0:c r="J54" s="313" t="str">
+        <ns0:v>quality</ns0:v>
+      </ns0:c>
+      <ns0:c r="K54" s="314" t="str">
+        <ns0:v>品质</ns0:v>
+      </ns0:c>
+      <ns0:c r="L54" s="315" t="str">
+        <ns0:v>Quality</ns0:v>
+      </ns0:c>
+      <ns0:c r="M54" s="316"/>
+      <ns0:c r="N54" s="317" t="str">
+        <ns0:v>本局兵种卡候选品质，不含普通</ns0:v>
+      </ns0:c>
+      <ns0:c r="O54" s="318"/>
+      <ns0:c r="P54" s="319"/>
+    </ns0:row>
+    <ns0:row spans="1:16" r="55">
+      <ns0:c r="A55" s="320"/>
+      <ns0:c r="B55" s="321"/>
+      <ns0:c r="C55" s="322"/>
+      <ns0:c r="D55" s="323"/>
+      <ns0:c r="E55" s="324"/>
+      <ns0:c r="F55" s="325"/>
+      <ns0:c r="G55" s="326"/>
+      <ns0:c r="H55" s="327"/>
+      <ns0:c r="I55" s="328"/>
+      <ns0:c r="J55" s="329" t="str">
+        <ns0:v>weight</ns0:v>
+      </ns0:c>
+      <ns0:c r="K55" s="330" t="str">
+        <ns0:v>权重</ns0:v>
+      </ns0:c>
+      <ns0:c r="L55" s="331" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M55" s="332"/>
+      <ns0:c r="N55" s="333" t="str">
+        <ns0:v>结果池相对权重；仅填正值</ns0:v>
+      </ns0:c>
+      <ns0:c r="O55" s="334"/>
+      <ns0:c r="P55" s="335"/>
+    </ns0:row>
+    <ns0:row r="57" ht="24" customHeight="1">
+      <ns0:c r="A57" s="48"/>
+      <ns0:c r="B57" s="49" t="str">
+        <ns0:v>bean.SkillEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="C57" s="50"/>
+      <ns0:c r="D57" s="51"/>
+      <ns0:c r="E57" s="52" t="str">
+        <ns0:v>,</ns0:v>
+      </ns0:c>
+      <ns0:c r="F57" s="53" t="str">
+        <ns0:v>技能效果</ns0:v>
+      </ns0:c>
+      <ns0:c r="G57" s="54"/>
+      <ns0:c r="H57" s="55"/>
+      <ns0:c r="I57" s="56"/>
+      <ns0:c r="J57" s="57"/>
+      <ns0:c r="K57" s="58"/>
+      <ns0:c r="L57" s="59"/>
+      <ns0:c r="M57" s="60"/>
+      <ns0:c r="N57" s="61"/>
+      <ns0:c r="O57" s="62"/>
+      <ns0:c r="P57" s="63"/>
+    </ns0:row>
+    <ns0:row r="58" ht="24" customHeight="1">
+      <ns0:c r="A58" s="48"/>
+      <ns0:c r="B58" s="49"/>
+      <ns0:c r="C58" s="50"/>
+      <ns0:c r="D58" s="51"/>
+      <ns0:c r="E58" s="52"/>
+      <ns0:c r="F58" s="53"/>
+      <ns0:c r="G58" s="54"/>
+      <ns0:c r="H58" s="55"/>
+      <ns0:c r="I58" s="56"/>
+      <ns0:c r="J58" s="57"/>
+      <ns0:c r="K58" s="58"/>
+      <ns0:c r="L58" s="59"/>
+      <ns0:c r="M58" s="60"/>
+      <ns0:c r="N58" s="61"/>
+      <ns0:c r="O58" s="62"/>
+      <ns0:c r="P58" s="63"/>
+    </ns0:row>
+    <ns0:row r="59" ht="24" customHeight="1">
+      <ns0:c r="A59" s="48"/>
+      <ns0:c r="B59" s="49" t="str">
+        <ns0:v>FixedDamageEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="C59" s="50" t="str">
+        <ns0:v>bean.SkillEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="D59" s="51"/>
+      <ns0:c r="E59" s="52" t="str">
+        <ns0:v>,</ns0:v>
+      </ns0:c>
+      <ns0:c r="F59" s="53" t="str">
+        <ns0:v>固定伤害</ns0:v>
+      </ns0:c>
+      <ns0:c r="G59" s="54"/>
+      <ns0:c r="H59" s="55"/>
+      <ns0:c r="I59" s="56"/>
+      <ns0:c r="J59" s="57" t="str">
+        <ns0:v>amount</ns0:v>
+      </ns0:c>
+      <ns0:c r="K59" s="58" t="str">
+        <ns0:v>伤害值</ns0:v>
+      </ns0:c>
+      <ns0:c r="L59" s="59" t="str">
+        <ns0:v>double</ns0:v>
+      </ns0:c>
+      <ns0:c r="M59" s="60"/>
+      <ns0:c r="N59" s="61" t="str">
+        <ns0:v>有限正数；生效时读取</ns0:v>
+      </ns0:c>
+      <ns0:c r="O59" s="62"/>
+      <ns0:c r="P59" s="63"/>
+    </ns0:row>
+    <ns0:row r="61" ht="24" customHeight="1">
+      <ns0:c r="B61" t="str" s="161">
+        <ns0:v>LaunchProjectileEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="C61" t="str" s="162">
+        <ns0:v>bean.SkillEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="D61" s="163"/>
+      <ns0:c r="E61" s="164"/>
+      <ns0:c r="F61" t="str" s="165">
+        <ns0:v>发射弹道</ns0:v>
+      </ns0:c>
+      <ns0:c r="G61" s="166"/>
+      <ns0:c r="H61" s="167"/>
+      <ns0:c r="I61" s="168"/>
+      <ns0:c r="J61" t="str" s="169">
+        <ns0:v>projectileId</ns0:v>
+      </ns0:c>
+      <ns0:c r="K61" t="str" s="170">
+        <ns0:v>弹道ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="L61" t="str" s="171">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="M61" s="172"/>
+      <ns0:c r="N61" t="str" s="173">
+        <ns0:v>引用ProjectileResource.id</ns0:v>
+      </ns0:c>
+      <ns0:c r="O61" s="174"/>
+      <ns0:c r="P61" s="175"/>
+    </ns0:row>
+    <ns0:row r="62" ht="24" customHeight="1">
+      <ns0:c r="B62" s="225"/>
+      <ns0:c r="C62" s="226"/>
+      <ns0:c r="D62" s="227"/>
+      <ns0:c r="E62" s="228"/>
+      <ns0:c r="F62" s="229"/>
+      <ns0:c r="G62" s="230"/>
+      <ns0:c r="H62" s="231"/>
+      <ns0:c r="I62" s="232"/>
+      <ns0:c r="J62" t="str" s="233">
+        <ns0:v>hitEffects</ns0:v>
+      </ns0:c>
+      <ns0:c r="K62" t="str" s="234">
+        <ns0:v>命中效果</ns0:v>
+      </ns0:c>
+      <ns0:c r="L62" t="str" s="235">
+        <ns0:v>(list#sep=;),bean.SkillEffect</ns0:v>
+      </ns0:c>
+      <ns0:c r="M62" s="236"/>
+      <ns0:c r="N62" t="str" s="237">
+        <ns0:v>发射时快照；首版固定伤害</ns0:v>
+      </ns0:c>
+      <ns0:c r="O62" s="238"/>
+      <ns0:c r="P62" s="239"/>
+    </ns0:row>
+    <ns0:row r="63" ht="25" customHeight="1">
+      <ns0:c r="J63" t="str" s="233">
+        <ns0:v>delayMs</ns0:v>
+      </ns0:c>
+      <ns0:c r="K63" t="str" s="234">
+        <ns0:v>发射延迟</ns0:v>
+      </ns0:c>
+      <ns0:c r="L63" t="str" s="235">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="N63" t="str" s="237">
+        <ns0:v>相对前摇结束，毫秒，必须落在后摇时间内</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="64" ht="24" customHeight="1">
+      <ns0:c r="J64" s="233" t="str">
+        <ns0:v>firePointIndex</ns0:v>
+      </ns0:c>
+      <ns0:c r="K64" s="234" t="str">
+        <ns0:v>挂点序号</ns0:v>
+      </ns0:c>
+      <ns0:c r="L64" s="235" t="str">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+      <ns0:c r="N64" s="237" t="str">
+        <ns0:v>同动作同源方向挂点的0起始序号</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="65" ht="24" customHeight="1"/>
+    <ns0:row r="66" ht="24" customHeight="1"/>
+    <ns0:row r="67" ht="25" customHeight="1"/>
+    <ns0:row r="68" ht="25" customHeight="1">
+      <ns0:c r="B68" t="str" s="161">
+        <ns0:v>bean.UnitFirePoint</ns0:v>
+      </ns0:c>
+      <ns0:c r="F68" t="str" s="165">
+        <ns0:v>单位发射挂点</ns0:v>
+      </ns0:c>
+      <ns0:c r="J68" t="str" s="169">
+        <ns0:v>action</ns0:v>
+      </ns0:c>
+      <ns0:c r="K68" t="str" s="170">
+        <ns0:v>动作</ns0:v>
+      </ns0:c>
+      <ns0:c r="L68" t="str" s="171">
+        <ns0:v>UnitActionType</ns0:v>
+      </ns0:c>
+      <ns0:c r="N68" t="str" s="173">
+        <ns0:v>对应攻击动作</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="69" ht="25" customHeight="1">
+      <ns0:c r="J69" t="str" s="185">
+        <ns0:v>direction</ns0:v>
+      </ns0:c>
+      <ns0:c r="K69" t="str" s="186">
+        <ns0:v>朝向</ns0:v>
+      </ns0:c>
+      <ns0:c r="L69" t="str" s="187">
+        <ns0:v>UnitAppearanceDirection</ns0:v>
+      </ns0:c>
+      <ns0:c r="N69" t="str" s="189">
+        <ns0:v>五方向源；左向镜像X</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="70" ht="25" customHeight="1">
+      <ns0:c r="J70" t="str" s="233">
+        <ns0:v>offset</ns0:v>
+      </ns0:c>
+      <ns0:c r="K70" t="str" s="234">
+        <ns0:v>偏移</ns0:v>
+      </ns0:c>
+      <ns0:c r="L70" t="str" s="235">
+        <ns0:v>vector2</ns0:v>
+      </ns0:c>
+      <ns0:c r="N70" t="str" s="237">
+        <ns0:v>相对脚底定位点；X右Y下</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:mergeCells count="1">
+    <ns0:mergeCell ref="J1:P1"/>
+  </ns0:mergeCells>
+  <ns0:conditionalFormatting sqref="$A1:$XFD1048576">
+    <ns0:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <ns0:formula>"bean.BattleLastingEffect"</ns0:formula>
+    </ns0:cfRule>
+    <ns0:cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <ns0:formula>"bean.Effect"</ns0:formula>
+    </ns0:cfRule>
+    <ns0:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <ns0:formula>"bean.Condition"</ns0:formula>
+    </ns0:cfRule>
+  </ns0:conditionalFormatting>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+  <ns0:dataValidations count="0"/>
+</ns0:worksheet>
 </file>